--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.43151061528823</v>
+        <v>5.432620474984337</v>
       </c>
       <c r="D2" t="n">
-        <v>31.10134788119057</v>
+        <v>5.053969030693467</v>
       </c>
       <c r="E2" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F2" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.76828057139726</v>
+        <v>8.899845592852056</v>
       </c>
       <c r="D3" t="n">
-        <v>42.57280654469962</v>
+        <v>6.918081063513689</v>
       </c>
       <c r="E3" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F3" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.40679826575635</v>
+        <v>10.46610471818541</v>
       </c>
       <c r="D4" t="n">
-        <v>44.60034219894333</v>
+        <v>7.247555607328292</v>
       </c>
       <c r="E4" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F4" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.79792987444778</v>
+        <v>5.817163604597765</v>
       </c>
       <c r="D5" t="n">
-        <v>12.9555216134859</v>
+        <v>2.105272262191459</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F5" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.80520027420241</v>
+        <v>8.093345044557891</v>
       </c>
       <c r="D6" t="n">
-        <v>10.00129923918518</v>
+        <v>1.625211126367591</v>
       </c>
       <c r="E6" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F6" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.67939339134907</v>
+        <v>8.397901426094224</v>
       </c>
       <c r="D7" t="n">
-        <v>16.50272260835614</v>
+        <v>2.681692423857874</v>
       </c>
       <c r="E7" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F7" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.81082520580465</v>
+        <v>10.69425909594326</v>
       </c>
       <c r="D8" t="n">
-        <v>24.63830901782297</v>
+        <v>4.003725215396233</v>
       </c>
       <c r="E8" t="n">
-        <v>11.67846092526969</v>
+        <v>1.897749900356325</v>
       </c>
       <c r="F8" t="n">
-        <v>12.89963406580013</v>
+        <v>2.096190535692521</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
